--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5327.8</v>
+        <v>5274.63</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>972.29</v>
+        <v>962.59</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1230</v>
+        <v>1217.12</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10547.35</v>
+        <v>10489.7</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>821.63</v>
+        <v>812.48</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1242.65</v>
+        <v>1235.85</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1866.97</v>
+        <v>1864.59</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14340.78</v>
+        <v>14588.32</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1068.01</v>
+        <v>1086.45</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7168.26</v>
+        <v>7292</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1104.57</v>
+        <v>1109.71</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>767.85</v>
+        <v>771.42</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1179.96</v>
+        <v>1188.46</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5990.86</v>
+        <v>5980.23</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23262.95</v>
+        <v>23221.69</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1066.63</v>
+        <v>1072.14</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3151.47</v>
+        <v>3173.71</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5457.53</v>
+        <v>5388.21</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5441.4</v>
+        <v>5429.62</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>934.23</v>
+        <v>926.3200000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>24948.5</v>
+        <v>25061.55</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2024.39</v>
+        <v>2021.55</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1091.07</v>
+        <v>1100.39</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6471.58</v>
+        <v>6541</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1388.68</v>
+        <v>1406.53</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>828.3200000000001</v>
+        <v>816.45</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1352.37</v>
+        <v>1332.99</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5639.59</v>
+        <v>5558.33</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4545.48</v>
+        <v>4660.39</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3792.26</v>
+        <v>3904.98</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9948.42</v>
+        <v>9977.24</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>819.1799999999999</v>
+        <v>823.41</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1158.45</v>
+        <v>1161.63</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5744.7</v>
+        <v>5796.95</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2955.74</v>
+        <v>2982.07</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3846.35</v>
+        <v>3839.75</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4224.54</v>
+        <v>4217.3</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6365.85</v>
+        <v>6359.29</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>17109.37</v>
+        <v>16986.8</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>848.72</v>
+        <v>847.47</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>811.5700000000001</v>
+        <v>807.15</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2273.03</v>
+        <v>2260.65</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3618.8</v>
+        <v>3599.09</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4907.64</v>
+        <v>4880.92</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8625.120000000001</v>
+        <v>8574.290000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7118.3</v>
+        <v>7075.05</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1523</v>
+        <v>1524.47</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7466.57</v>
+        <v>7484.94</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1444.15</v>
+        <v>1447.7</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2971.95</v>
+        <v>2979.26</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2216.73</v>
+        <v>2222.19</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4039.87</v>
+        <v>3987.86</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1911.2</v>
+        <v>1897.71</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>855.6</v>
+        <v>855.5599999999999</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6646.77</v>
+        <v>6652.5</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>945.13</v>
+        <v>945.9400000000001</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8225.530000000001</v>
+        <v>8232.620000000001</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3773</v>
+        <v>3788.59</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7086.97</v>
+        <v>7067.42</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7859.22</v>
+        <v>7837.54</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1382.25</v>
+        <v>1374.31</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1999.46</v>
+        <v>1987.98</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2599.46</v>
+        <v>2584.53</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>848</v>
+        <v>843.13</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2817.48</v>
+        <v>2801.29</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2232.27</v>
+        <v>2217.96</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1861.07</v>
+        <v>1853.05</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>775.03</v>
+        <v>763.8200000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1426.45</v>
+        <v>1405.81</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1067.52</v>
+        <v>1038.93</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2542.57</v>
+        <v>2564.15</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2369.7</v>
+        <v>2365.74</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2084.09</v>
+        <v>2080.6</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7336.77</v>
+        <v>7324.5</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1829.36</v>
+        <v>1851.87</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>864.84</v>
+        <v>875.48</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3823.46</v>
+        <v>3870.52</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2292.51</v>
+        <v>2323.03</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1753.6</v>
+        <v>1786.77</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1450.56</v>
+        <v>1467.05</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2175.27</v>
+        <v>2184.29</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1307.21</v>
+        <v>1299.37</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1594.42</v>
+        <v>1603.01</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1105.53</v>
+        <v>1094.51</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1015.33</v>
+        <v>1012.82</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>923.36</v>
+        <v>921.08</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3939.19</v>
+        <v>3952.26</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1382.43</v>
+        <v>1386.83</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11720.7</v>
+        <v>11918.93</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1064.46</v>
+        <v>1075.28</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1459.57</v>
+        <v>1434.91</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3589.9</v>
+        <v>3529.25</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3240.48</v>
+        <v>3195.96</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6164.82</v>
+        <v>6126.6</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>989.01</v>
+        <v>1011.31</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>10057.4</v>
+        <v>9923.43</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1242.22</v>
+        <v>1217.91</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>21688.17</v>
+        <v>21366.84</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1036.68</v>
+        <v>1040.72</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>920.11</v>
+        <v>923.7</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3798.15</v>
+        <v>3812.94</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1106.31</v>
+        <v>1110.62</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>799.15</v>
+        <v>795.1</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2953.47</v>
+        <v>2960.24</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2065.25</v>
+        <v>2061.11</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2066.4</v>
+        <v>2054.44</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1028.31</v>
+        <v>1011.71</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1278.28</v>
+        <v>1257.79</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,68 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5199.99</v>
+        <v>5234.8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>5593-126-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>2824.68</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1075963-51885-CM25</t>
+          <t>1075963-22382-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5274.63</v>
+        <v>5256.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1572-318-CM25</t>
+          <t>707409-70-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>962.59</v>
+        <v>1879.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5358-434-CM25</t>
+          <t>1110404-1055-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1217.12</v>
+        <v>71411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2585-4456-CM25</t>
+          <t>1075963-51885-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10489.7</v>
+        <v>5274.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5951-5597-CM25</t>
+          <t>1572-318-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>812.48</v>
+        <v>962.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1110404-1496-CM25</t>
+          <t>5358-434-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1235.85</v>
+        <v>1217.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5360-416-CM25</t>
+          <t>2585-4456-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1864.59</v>
+        <v>10489.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2366-4364-CM25</t>
+          <t>5951-5597-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14588.32</v>
+        <v>812.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>720-547-CM25</t>
+          <t>1110404-1496-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1086.45</v>
+        <v>1235.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5750-123-CM25</t>
+          <t>5360-416-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7292</v>
+        <v>1864.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>635-4839-CM25</t>
+          <t>720-547-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1109.71</v>
+        <v>1086.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>635-4854-CM25</t>
+          <t>5750-123-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>771.42</v>
+        <v>7292</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>720-548-CM25</t>
+          <t>2366-4364-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1188.46</v>
+        <v>14588.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079596-370-CM25</t>
+          <t>635-4839-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5980.23</v>
+        <v>1109.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1093870-20-CM25</t>
+          <t>635-4854-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23221.69</v>
+        <v>771.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1079596-372-CM25</t>
+          <t>720-548-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1072.14</v>
+        <v>1188.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5739-22-CM25</t>
+          <t>1093870-20-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3173.71</v>
+        <v>23221.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1079596-386-CM25</t>
+          <t>1079596-370-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5388.21</v>
+        <v>5980.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1075963-56396-CM25</t>
+          <t>1079596-372-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5429.62</v>
+        <v>1072.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>720-1123-CM25</t>
+          <t>5739-22-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>926.3200000000001</v>
+        <v>3173.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1572-370-CM25</t>
+          <t>1079596-386-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.955.038-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>25061.55</v>
+        <v>5388.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2585-4704-CM25</t>
+          <t>1075963-56396-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2021.55</v>
+        <v>5429.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5649-46-CM25</t>
+          <t>720-1123-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1100.39</v>
+        <v>926.3200000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5750-144-CM25</t>
+          <t>1572-370-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.955.038-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6541</v>
+        <v>25061.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1572-398-CM25</t>
+          <t>2585-4704-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1406.53</v>
+        <v>2021.55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>707409-1-CM26</t>
+          <t>5649-46-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>816.45</v>
+        <v>1100.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>707409-2-CM26</t>
+          <t>5750-144-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1332.99</v>
+        <v>6541</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1075963-491-CM26</t>
+          <t>1572-398-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5558.33</v>
+        <v>1406.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>635-64-CM26</t>
+          <t>707409-2-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4660.39</v>
+        <v>1332.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1151549-17-CM26</t>
+          <t>707409-1-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,22 +2298,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3904.98</v>
+        <v>816.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1084148-13-CM26</t>
+          <t>1075963-491-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9977.24</v>
+        <v>5558.33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1110404-55-CM26</t>
+          <t>635-64-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>823.41</v>
+        <v>4660.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5702-75-CM26</t>
+          <t>1151549-17-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1161.63</v>
+        <v>3904.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5360-54-CM26</t>
+          <t>1084148-13-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5796.95</v>
+        <v>9977.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1696-24-CM26</t>
+          <t>1110404-55-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,22 +2603,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2982.07</v>
+        <v>823.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1346279-20-CM26</t>
+          <t>5702-75-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3839.75</v>
+        <v>1161.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1075963-2359-CM26</t>
+          <t>5360-54-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4217.3</v>
+        <v>5796.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3348-17-CM26</t>
+          <t>1696-24-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,22 +2786,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6359.29</v>
+        <v>2982.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079596-25-CM26</t>
+          <t>1346279-20-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>16986.8</v>
+        <v>3839.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3340-22-CM26</t>
+          <t>1075963-2359-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>847.47</v>
+        <v>4217.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1572-12-CM26</t>
+          <t>3348-17-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>807.15</v>
+        <v>6359.29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1572-11-CM26</t>
+          <t>1079596-25-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2260.65</v>
+        <v>16986.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1075963-2497-CM26</t>
+          <t>3340-22-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3599.09</v>
+        <v>847.47</v>
       </c>
     </row>
     <row r="45">
@@ -3198,7 +3198,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1346279-22-CM26</t>
+          <t>1075963-2497-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8574.290000000001</v>
+        <v>3599.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1084148-24-CM26</t>
+          <t>1572-11-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7075.05</v>
+        <v>2260.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>812690-7-CM26</t>
+          <t>1572-12-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1524.47</v>
+        <v>807.15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2366-100-CM26</t>
+          <t>1346279-22-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7484.94</v>
+        <v>8574.290000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2366-107-CM26</t>
+          <t>1084148-24-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1447.7</v>
+        <v>7075.05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5420-18-CM26</t>
+          <t>812690-7-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,27 +3513,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2979.26</v>
+        <v>1524.47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5420-19-CM26</t>
+          <t>2366-100-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2222.19</v>
+        <v>7484.94</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5611-27-CM26</t>
+          <t>2366-107-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3987.86</v>
+        <v>1447.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5473-18-CM26</t>
+          <t>5420-18-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.978.970-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1897.71</v>
+        <v>2979.26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5649-11-CM26</t>
+          <t>5420-19-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>855.5599999999999</v>
+        <v>2222.19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1572-26-CM26</t>
+          <t>5611-27-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6652.5</v>
+        <v>3987.86</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1572-25-CM26</t>
+          <t>5473-18-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>945.9400000000001</v>
+        <v>1897.71</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5687-12-CM26</t>
+          <t>5649-11-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.978.920-2</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACIONES REGION ARICA-PARINACOTA</t>
+          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8232.620000000001</v>
+        <v>855.5599999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1075963-3858-CM26</t>
+          <t>1572-25-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3788.59</v>
+        <v>945.9400000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3459-48-CM26</t>
+          <t>5687-12-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.978.920-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACIONES REGION ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7067.42</v>
+        <v>8232.620000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1774-31-CM26</t>
+          <t>1572-26-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7837.54</v>
+        <v>6652.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1110404-197-CM26</t>
+          <t>1075963-3858-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1374.31</v>
+        <v>3788.59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1110404-199-CM26</t>
+          <t>3459-48-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1987.98</v>
+        <v>7067.42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1110404-200-CM26</t>
+          <t>1774-31-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2584.53</v>
+        <v>7837.54</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1110404-201-CM26</t>
+          <t>1110404-197-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>843.13</v>
+        <v>1374.31</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1110404-202-CM26</t>
+          <t>1110404-199-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.473.108-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2801.29</v>
+        <v>1987.98</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4232-34-CM26</t>
+          <t>1110404-200-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2217.96</v>
+        <v>2584.53</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3185-41-CM26</t>
+          <t>1110404-201-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1853.05</v>
+        <v>843.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>707409-38-CM26</t>
+          <t>1110404-202-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>INVERSIONES CORP PREMIER LTDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>76.473.108-5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>763.8200000000001</v>
+        <v>2801.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>707409-37-CM26</t>
+          <t>4232-34-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1405.81</v>
+        <v>2217.96</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1173457-12-CM26</t>
+          <t>3185-41-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>GOBERNACION MARITIMA DE ARICA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1038.93</v>
+        <v>1853.05</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1110404-295-CM26</t>
+          <t>707409-38-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2564.15</v>
+        <v>763.8200000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5420-34-CM26</t>
+          <t>707409-37-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2365.74</v>
+        <v>1405.81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5420-35-CM26</t>
+          <t>1173457-12-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2080.6</v>
+        <v>1038.93</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2021-66-CM26</t>
+          <t>1110404-295-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7324.5</v>
+        <v>2564.15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2366-199-CM26</t>
+          <t>5420-34-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1851.87</v>
+        <v>2365.74</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3390-128-CM26</t>
+          <t>5420-35-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>875.48</v>
+        <v>2080.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1075963-5093-CM26</t>
+          <t>2021-66-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3870.52</v>
+        <v>7324.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2585-284-CM26</t>
+          <t>2366-199-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2323.03</v>
+        <v>1851.87</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2585-297-CM26</t>
+          <t>3390-128-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1786.77</v>
+        <v>875.48</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1110404-330-CM26</t>
+          <t>1075963-5093-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1467.05</v>
+        <v>3870.52</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>548849-44-CM26</t>
+          <t>2585-284-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2184.29</v>
+        <v>2323.03</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1110404-368-CM26</t>
+          <t>2585-297-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1299.37</v>
+        <v>1786.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>720-109-CM26</t>
+          <t>1110404-330-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1603.01</v>
+        <v>1467.05</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1151549-97-CM26</t>
+          <t>548849-44-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1094.51</v>
+        <v>2184.29</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1347870-40-CM26</t>
+          <t>1110404-368-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1012.82</v>
+        <v>1299.37</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5550-17-CM26</t>
+          <t>720-109-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>921.08</v>
+        <v>1603.01</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1075963-6998-CM26</t>
+          <t>1151549-97-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3952.26</v>
+        <v>1094.51</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5702-368-CM26</t>
+          <t>1347870-40-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1386.83</v>
+        <v>1012.82</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2585-456-CM26</t>
+          <t>5550-17-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,27 +5892,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11918.93</v>
+        <v>921.08</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>635-725-CM26</t>
+          <t>1075963-6998-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,27 +5953,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1075.28</v>
+        <v>3952.26</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5611-48-CM26</t>
+          <t>5702-368-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1434.91</v>
+        <v>1386.83</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5611-49-CM26</t>
+          <t>2585-456-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3529.25</v>
+        <v>11918.93</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1110404-515-CM26</t>
+          <t>635-725-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3195.96</v>
+        <v>1075.28</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1696-172-CM26</t>
+          <t>5611-48-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,22 +6202,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6126.6</v>
+        <v>1434.91</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1084148-59-CM26</t>
+          <t>5611-49-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,22 +6263,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1011.31</v>
+        <v>3529.25</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1093870-8-CM26</t>
+          <t>1110404-515-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>9923.43</v>
+        <v>3195.96</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1572-61-CM26</t>
+          <t>1696-172-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,22 +6385,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1217.91</v>
+        <v>6126.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2585-595-CM26</t>
+          <t>1084148-59-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>21366.84</v>
+        <v>1011.31</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>707409-66-CM26</t>
+          <t>1093870-8-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1040.72</v>
+        <v>9923.43</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>707409-67-CM26</t>
+          <t>1572-61-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>923.7</v>
+        <v>1217.91</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1075963-8316-CM26</t>
+          <t>2585-595-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,27 +6624,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3812.94</v>
+        <v>21366.84</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5702-496-CM26</t>
+          <t>707409-66-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,22 +6690,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1110.62</v>
+        <v>1040.72</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5951-78-CM26</t>
+          <t>707409-67-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,22 +6751,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>795.1</v>
+        <v>923.7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5611-65-CM26</t>
+          <t>1075963-8316-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2960.24</v>
+        <v>3812.94</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1110404-670-CM26</t>
+          <t>5702-496-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,22 +6873,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2061.11</v>
+        <v>1110.62</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1110404-658-CM26</t>
+          <t>5951-78-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,22 +6934,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2054.44</v>
+        <v>795.1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1108734-36-CM26</t>
+          <t>5611-65-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1011.71</v>
+        <v>2960.24</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2021-147-CM26</t>
+          <t>1110404-670-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1257.79</v>
+        <v>2061.11</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1075963-10005-CM26</t>
+          <t>1110404-658-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,22 +7117,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5234.8</v>
+        <v>2054.44</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5593-126-CM26</t>
+          <t>1108734-36-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,27 +7173,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,6 +7218,189 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
+        <v>1011.71</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2021-147-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>61.101.040-0</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Estado Mayor Conjunto</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>1257.79</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1075963-10005-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>5234.8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>5593-126-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
         <v>2824.68</v>
       </c>
     </row>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1075963-22382-CM25</t>
+          <t>1110404-755-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>COMERCIALIZADORA MALUSANT SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.720.988-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5256.83</v>
+        <v>2040.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>707409-70-CM25</t>
+          <t>1075963-22382-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1879.84</v>
+        <v>5256.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1110404-1055-CM25</t>
+          <t>707409-70-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>71411</v>
+        <v>1879.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1075963-51885-CM25</t>
+          <t>5360-275-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5274.63</v>
+        <v>3197.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1572-318-CM25</t>
+          <t>5702-534-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>962.59</v>
+        <v>4107.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5358-434-CM25</t>
+          <t>837-379-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1217.12</v>
+        <v>4777.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2585-4456-CM25</t>
+          <t>1110404-954-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10489.7</v>
+        <v>4665.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5951-5597-CM25</t>
+          <t>3390-276-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>812.48</v>
+        <v>932.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1110404-1496-CM25</t>
+          <t>4232-94-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1235.85</v>
+        <v>760.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5360-416-CM25</t>
+          <t>1075963-23622-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1864.59</v>
+        <v>4268.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>720-547-CM25</t>
+          <t>1110404-997-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1086.45</v>
+        <v>6509.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5750-123-CM25</t>
+          <t>5593-128-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7292</v>
+        <v>1329.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2366-4364-CM25</t>
+          <t>1110404-1019-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>14588.32</v>
+        <v>70388.00999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>635-4839-CM25</t>
+          <t>5611-95-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1109.71</v>
+        <v>2321.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>635-4854-CM25</t>
+          <t>1110404-1018-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>771.42</v>
+        <v>70119.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>720-548-CM25</t>
+          <t>1110404-1021-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1188.46</v>
+        <v>10319.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1093870-20-CM25</t>
+          <t>1110404-1022-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>23221.69</v>
+        <v>70614.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1079596-370-CM25</t>
+          <t>1110404-1055-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5980.23</v>
+        <v>71411</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1079596-372-CM25</t>
+          <t>1151549-278-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1072.14</v>
+        <v>2383.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5739-22-CM25</t>
+          <t>1151549-279-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3173.71</v>
+        <v>765.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1079596-386-CM25</t>
+          <t>1337362-51-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5388.21</v>
+        <v>730.0599999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1075963-56396-CM25</t>
+          <t>2585-4142-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5429.62</v>
+        <v>4758.88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>720-1123-CM25</t>
+          <t>1075963-32417-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>926.3200000000001</v>
+        <v>4977.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1572-370-CM25</t>
+          <t>635-4071-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.955.038-0</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>25061.55</v>
+        <v>3055.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2585-4704-CM25</t>
+          <t>2585-4203-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2021.55</v>
+        <v>1213.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5649-46-CM25</t>
+          <t>707409-101-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1100.39</v>
+        <v>1868.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5750-144-CM25</t>
+          <t>1079596-267-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6541</v>
+        <v>2240.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1572-398-CM25</t>
+          <t>707409-107-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1406.53</v>
+        <v>1284.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>707409-2-CM26</t>
+          <t>707409-108-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1332.99</v>
+        <v>1645.78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>707409-1-CM26</t>
+          <t>2369-64-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2331,20 +2331,24 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>816.45</v>
+        <v>52649.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1075963-491-CM26</t>
+          <t>1346279-186-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2358,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5558.33</v>
+        <v>1455.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>635-64-CM26</t>
+          <t>5687-54-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2419,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2434,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.978.920-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4660.39</v>
+        <v>2145.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1151549-17-CM26</t>
+          <t>5750-105-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2480,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3904.98</v>
+        <v>4774.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1084148-13-CM26</t>
+          <t>2366-4277-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2541,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2556,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2571,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>9977.24</v>
+        <v>5727.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1110404-55-CM26</t>
+          <t>5702-806-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2602,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>823.41</v>
+        <v>913.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5702-75-CM26</t>
+          <t>2585-4373-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2663,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2693,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1161.63</v>
+        <v>12432.74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5360-54-CM26</t>
+          <t>2585-4267-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2724,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5796.95</v>
+        <v>2165.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1696-24-CM26</t>
+          <t>720-502-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2785,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2982.07</v>
+        <v>3824.88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1346279-20-CM26</t>
+          <t>5420-294-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2846,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2861,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3839.75</v>
+        <v>1491.88</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1075963-2359-CM26</t>
+          <t>2366-4297-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,27 +2907,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4217.3</v>
+        <v>12687.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3348-17-CM26</t>
+          <t>1075963-51885-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,27 +2968,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2998,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6359.29</v>
+        <v>5274.63</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1079596-25-CM26</t>
+          <t>1572-318-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3029,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3044,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3059,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16986.8</v>
+        <v>962.59</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3340-22-CM26</t>
+          <t>5358-434-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3090,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3120,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>847.47</v>
+        <v>1217.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3390-45-CM26</t>
+          <t>2585-4456-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3151,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3181,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4880.92</v>
+        <v>10489.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1075963-2497-CM26</t>
+          <t>5951-5597-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3212,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3242,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3599.09</v>
+        <v>812.48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1572-11-CM26</t>
+          <t>1110404-1496-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3273,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3288,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2260.65</v>
+        <v>1235.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1572-12-CM26</t>
+          <t>5360-416-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,27 +3334,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>807.15</v>
+        <v>1864.59</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1346279-22-CM26</t>
+          <t>5750-123-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3395,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3410,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8574.290000000001</v>
+        <v>7292</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1084148-24-CM26</t>
+          <t>720-547-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3456,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3486,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7075.05</v>
+        <v>1086.45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>812690-7-CM26</t>
+          <t>2366-4364-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,27 +3517,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3547,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1524.47</v>
+        <v>14588.32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2366-100-CM26</t>
+          <t>635-4839-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3578,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3608,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7484.94</v>
+        <v>1109.71</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2366-107-CM26</t>
+          <t>635-4854-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3639,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3654,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3669,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1447.7</v>
+        <v>771.42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5420-18-CM26</t>
+          <t>720-548-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3700,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3715,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3730,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2979.26</v>
+        <v>1188.46</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5420-19-CM26</t>
+          <t>1093870-20-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3761,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3776,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3791,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2222.19</v>
+        <v>23221.69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5611-27-CM26</t>
+          <t>1079596-370-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3822,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3837,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3987.86</v>
+        <v>5980.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5473-18-CM26</t>
+          <t>1079596-372-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3883,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3898,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.978.970-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1897.71</v>
+        <v>1072.14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5649-11-CM26</t>
+          <t>5739-22-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3944,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>855.5599999999999</v>
+        <v>3173.71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1572-25-CM26</t>
+          <t>1079596-386-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4005,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>945.9400000000001</v>
+        <v>5388.21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5687-12-CM26</t>
+          <t>1075963-56396-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4066,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4081,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.978.920-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACIONES REGION ARICA-PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>8232.620000000001</v>
+        <v>5429.62</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1572-26-CM26</t>
+          <t>720-1123-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4127,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4157,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6652.5</v>
+        <v>926.3200000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1075963-3858-CM26</t>
+          <t>1572-370-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4188,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4203,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.955.038-0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3788.59</v>
+        <v>25061.55</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3459-48-CM26</t>
+          <t>2585-4704-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4249,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4264,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4279,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7067.42</v>
+        <v>2021.55</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1774-31-CM26</t>
+          <t>5649-46-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4310,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4325,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4340,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>7837.54</v>
+        <v>1100.39</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1110404-197-CM26</t>
+          <t>5750-144-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4371,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4386,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4401,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1374.31</v>
+        <v>6541</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1110404-199-CM26</t>
+          <t>1572-398-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4432,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4447,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4462,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1987.98</v>
+        <v>1406.53</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1110404-200-CM26</t>
+          <t>707409-2-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4493,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4508,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4523,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2584.53</v>
+        <v>1332.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1110404-201-CM26</t>
+          <t>707409-1-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4554,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4569,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4584,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>843.13</v>
+        <v>816.45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1110404-202-CM26</t>
+          <t>1075963-491-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,27 +4615,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4645,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.473.108-5</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2801.29</v>
+        <v>5558.33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4232-34-CM26</t>
+          <t>635-64-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4676,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4691,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4706,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2217.96</v>
+        <v>4660.39</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3185-41-CM26</t>
+          <t>1151549-17-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,27 +4737,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4767,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1853.05</v>
+        <v>3904.98</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>707409-38-CM26</t>
+          <t>1084148-13-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4798,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4813,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4828,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>763.8200000000001</v>
+        <v>9977.24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>707409-37-CM26</t>
+          <t>1110404-55-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4859,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4874,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4889,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1405.81</v>
+        <v>823.41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1173457-12-CM26</t>
+          <t>5702-75-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,27 +4920,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4950,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1038.93</v>
+        <v>1161.63</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1110404-295-CM26</t>
+          <t>5360-54-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,27 +4981,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2564.15</v>
+        <v>5796.95</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5420-34-CM26</t>
+          <t>1696-24-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,27 +5042,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5072,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2365.74</v>
+        <v>2982.07</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5420-35-CM26</t>
+          <t>1075963-2359-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,27 +5103,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5133,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2080.6</v>
+        <v>4217.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2021-66-CM26</t>
+          <t>1346279-20-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5164,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5179,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5194,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7324.5</v>
+        <v>3839.75</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2366-199-CM26</t>
+          <t>3348-17-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5225,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5240,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5255,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1851.87</v>
+        <v>6359.29</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3390-128-CM26</t>
+          <t>1079596-25-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,12 +5286,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5301,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5316,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>875.48</v>
+        <v>16986.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1075963-5093-CM26</t>
+          <t>3340-22-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,12 +5347,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5362,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5377,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3870.52</v>
+        <v>847.47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2585-284-CM26</t>
+          <t>3390-45-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,12 +5408,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5423,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5438,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2323.03</v>
+        <v>4880.92</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2585-297-CM26</t>
+          <t>1075963-2497-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5469,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5484,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5499,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1786.77</v>
+        <v>3599.09</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1110404-330-CM26</t>
+          <t>1572-11-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,12 +5530,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5545,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5560,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1467.05</v>
+        <v>2260.65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>548849-44-CM26</t>
+          <t>1572-12-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,27 +5591,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5636,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2184.29</v>
+        <v>807.15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1110404-368-CM26</t>
+          <t>1346279-22-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,12 +5652,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5667,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5682,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5697,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1299.37</v>
+        <v>8574.290000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>720-109-CM26</t>
+          <t>1084148-24-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5713,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5728,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5743,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1603.01</v>
+        <v>7075.05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1151549-97-CM26</t>
+          <t>812690-7-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5774,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5789,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1094.51</v>
+        <v>1524.47</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1347870-40-CM26</t>
+          <t>2366-100-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5835,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5861,12 +5865,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1012.82</v>
+        <v>7484.94</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5550-17-CM26</t>
+          <t>2366-107-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5896,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5911,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>921.08</v>
+        <v>1447.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1075963-6998-CM26</t>
+          <t>5420-18-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,27 +5957,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5987,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3952.26</v>
+        <v>2979.26</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5702-368-CM26</t>
+          <t>5420-19-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6018,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6033,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6048,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1386.83</v>
+        <v>2222.19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2585-456-CM26</t>
+          <t>5611-27-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,27 +6079,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6109,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>11918.93</v>
+        <v>3987.86</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>635-725-CM26</t>
+          <t>5473-18-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6140,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6155,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1075.28</v>
+        <v>1897.71</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5611-48-CM26</t>
+          <t>5649-11-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,12 +6201,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6216,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6231,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6246,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1434.91</v>
+        <v>855.5599999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5611-49-CM26</t>
+          <t>1572-26-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,27 +6262,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6292,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6307,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3529.25</v>
+        <v>6652.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1110404-515-CM26</t>
+          <t>5687-12-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,12 +6323,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6338,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.978.920-2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACIONES REGION ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6353,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6368,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3195.96</v>
+        <v>8232.620000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1696-172-CM26</t>
+          <t>1572-25-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,27 +6384,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6414,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>6126.6</v>
+        <v>945.9400000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1084148-59-CM26</t>
+          <t>1075963-3858-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6445,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6475,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6490,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1011.31</v>
+        <v>3788.59</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1093870-8-CM26</t>
+          <t>3459-48-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6506,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6521,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6536,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>9923.43</v>
+        <v>7067.42</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1572-61-CM26</t>
+          <t>1774-31-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6567,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6582,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1217.91</v>
+        <v>7837.54</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2585-595-CM26</t>
+          <t>1110404-197-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,12 +6628,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6643,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6658,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>21366.84</v>
+        <v>1374.31</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>707409-66-CM26</t>
+          <t>1110404-199-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6689,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6704,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6719,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6734,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1040.72</v>
+        <v>1987.98</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>707409-67-CM26</t>
+          <t>1110404-200-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6750,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6765,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6780,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6795,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>923.7</v>
+        <v>2584.53</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1075963-8316-CM26</t>
+          <t>1110404-201-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,27 +6811,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6841,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3812.94</v>
+        <v>843.13</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5702-496-CM26</t>
+          <t>1110404-202-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6868,27 +6872,27 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6902,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>INVERSIONES CORP PREMIER LTDA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.473.108-5</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1110.62</v>
+        <v>2801.29</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5951-78-CM26</t>
+          <t>4232-34-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,27 +6933,27 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6963,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>795.1</v>
+        <v>2217.96</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5611-65-CM26</t>
+          <t>3185-41-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,27 +6994,27 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>GOBERNACION MARITIMA DE ARICA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7024,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2960.24</v>
+        <v>1853.05</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1110404-670-CM26</t>
+          <t>707409-37-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,12 +7055,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7070,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7085,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2061.11</v>
+        <v>1405.81</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1110404-658-CM26</t>
+          <t>707409-38-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7112,12 +7116,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7131,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7146,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2054.44</v>
+        <v>763.8200000000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1108734-36-CM26</t>
+          <t>1173457-12-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,27 +7177,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7207,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1011.71</v>
+        <v>1038.93</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2021-147-CM26</t>
+          <t>1110404-295-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7234,12 +7238,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7253,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7268,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1257.79</v>
+        <v>2564.15</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1075963-10005-CM26</t>
+          <t>5420-34-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7295,27 +7299,27 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7329,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5234.8</v>
+        <v>2365.74</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5593-126-CM26</t>
+          <t>5420-35-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7356,12 +7360,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,12 +7375,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7390,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,7 +7405,2508 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
+        <v>2080.6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2021-66-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.101.040-0</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Estado Mayor Conjunto</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>7324.5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1075963-5093-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>3870.52</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2366-199-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>78.067.906-9</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>1851.87</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>3390-128-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>875.48</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2585-284-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>2323.03</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2585-297-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>1786.77</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1110404-330-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>1467.05</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>548849-44-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>61.979.440-0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Instituto de Prevision Social</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>2184.29</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1110404-368-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>1299.37</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>720-109-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>1603.01</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1151549-97-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>53.333.710-4</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>1094.51</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>5550-17-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>61.533.000-0</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>921.08</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1347870-40-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>1012.82</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1075963-6998-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>3952.26</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>5702-368-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>1386.83</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2585-456-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>11918.93</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>635-725-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>1075.28</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>5611-48-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>61.813.000-2</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>1434.91</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>5611-49-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>61.813.000-2</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>3529.25</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1110404-515-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>3195.96</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1696-172-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>6126.6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1084148-59-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>1011.31</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1093870-8-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>65.184.303-0</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>9923.43</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1572-61-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>1217.91</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2585-595-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>21366.84</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>707409-66-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>1040.72</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>707409-67-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>923.7</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1075963-8316-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>3812.94</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>5702-496-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>1110.62</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>5951-78-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>795.1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>5611-65-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>61.813.000-2</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>2960.24</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1110404-670-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>2061.11</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1110404-658-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>2054.44</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1108734-36-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>1011.71</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2021-147-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>61.101.040-0</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Estado Mayor Conjunto</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>1257.79</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1075963-10005-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>5234.8</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>5593-126-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
         <v>2824.68</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>5611-73-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>61.813.000-2</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>1582.48</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>635-1139-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>1007.13</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1110404-839-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>3207.31</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1173041-42-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>70.456.600-K</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>959.4299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1246,7 +1246,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1110404-1019-CM25</t>
+          <t>5611-95-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>70388.00999999999</v>
+        <v>2321.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5611-95-CM25</t>
+          <t>1110404-1018-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2321.42</v>
+        <v>70119.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1110404-1018-CM25</t>
+          <t>1110404-1021-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>70119.28</v>
+        <v>10319.58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1110404-1021-CM25</t>
+          <t>1110404-1022-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10319.58</v>
+        <v>70614.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1110404-1022-CM25</t>
+          <t>1110404-1019-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>70614.41</v>
+        <v>70388.00999999999</v>
       </c>
     </row>
     <row r="19">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3751,7 +3751,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1093870-20-CM25</t>
+          <t>1079596-370-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>23221.69</v>
+        <v>5980.23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1079596-370-CM25</t>
+          <t>1093870-20-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5980.23</v>
+        <v>23221.69</v>
       </c>
     </row>
     <row r="57">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3934,7 +3934,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5739-22-CM25</t>
+          <t>1079596-386-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3173.71</v>
+        <v>5388.21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1079596-386-CM25</t>
+          <t>1075963-56396-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5388.21</v>
+        <v>5429.62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1075963-56396-CM25</t>
+          <t>720-1123-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5429.62</v>
+        <v>926.3200000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>720-1123-CM25</t>
+          <t>1572-370-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.955.038-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>926.3200000000001</v>
+        <v>25061.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1572-370-CM25</t>
+          <t>2585-4704-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.955.038-0</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>25061.55</v>
+        <v>2021.55</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2585-4704-CM25</t>
+          <t>5649-46-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2021.55</v>
+        <v>1100.39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5649-46-CM25</t>
+          <t>5750-144-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1100.39</v>
+        <v>6541</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5750-144-CM25</t>
+          <t>1572-398-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6541</v>
+        <v>1406.53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1572-398-CM25</t>
+          <t>707409-1-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1406.53</v>
+        <v>816.45</v>
       </c>
     </row>
     <row r="67">
@@ -4544,7 +4544,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>707409-1-CM26</t>
+          <t>1075963-491-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4559,22 +4559,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>816.45</v>
+        <v>5558.33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1075963-491-CM26</t>
+          <t>635-64-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4620,22 +4620,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5558.33</v>
+        <v>4660.39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>635-64-CM26</t>
+          <t>1151549-17-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4681,22 +4681,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4660.39</v>
+        <v>3904.98</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1151549-17-CM26</t>
+          <t>1084148-13-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4737,27 +4737,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3904.98</v>
+        <v>9977.24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1084148-13-CM26</t>
+          <t>1110404-55-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9977.24</v>
+        <v>823.41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1110404-55-CM26</t>
+          <t>5702-75-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4864,22 +4864,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>823.41</v>
+        <v>1161.63</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5702-75-CM26</t>
+          <t>5360-54-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1161.63</v>
+        <v>5796.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5360-54-CM26</t>
+          <t>1696-24-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5026,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5796.95</v>
+        <v>2982.07</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1696-24-CM26</t>
+          <t>1346279-20-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5047,22 +5047,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2982.07</v>
+        <v>3839.75</v>
       </c>
     </row>
     <row r="77">
@@ -5154,7 +5154,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1346279-20-CM26</t>
+          <t>3348-17-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3839.75</v>
+        <v>6359.29</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3348-17-CM26</t>
+          <t>1079596-25-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>6359.29</v>
+        <v>16986.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1079596-25-CM26</t>
+          <t>3340-22-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>16986.8</v>
+        <v>847.47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3340-22-CM26</t>
+          <t>1572-12-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>847.47</v>
+        <v>807.15</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3390-45-CM26</t>
+          <t>1572-11-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4880.92</v>
+        <v>2260.65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1075963-2497-CM26</t>
+          <t>3390-45-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3599.09</v>
+        <v>4880.92</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1572-11-CM26</t>
+          <t>1075963-2497-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2260.65</v>
+        <v>3599.09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1572-12-CM26</t>
+          <t>1346279-22-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5606,12 +5606,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>807.15</v>
+        <v>8574.290000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1346279-22-CM26</t>
+          <t>1084148-24-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>8574.290000000001</v>
+        <v>7075.05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1084148-24-CM26</t>
+          <t>812690-7-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5718,22 +5718,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7075.05</v>
+        <v>1524.47</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>812690-7-CM26</t>
+          <t>2366-100-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5774,27 +5774,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1524.47</v>
+        <v>7484.94</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2366-100-CM26</t>
+          <t>2366-107-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7484.94</v>
+        <v>1447.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2366-107-CM26</t>
+          <t>5420-18-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1447.7</v>
+        <v>2979.26</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5420-18-CM26</t>
+          <t>5420-19-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2979.26</v>
+        <v>2222.19</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5420-19-CM26</t>
+          <t>5611-27-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2222.19</v>
+        <v>3987.86</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5611-27-CM26</t>
+          <t>5473-18-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3987.86</v>
+        <v>1897.71</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5473-18-CM26</t>
+          <t>5649-11-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.978.970-9</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1897.71</v>
+        <v>855.5599999999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5649-11-CM26</t>
+          <t>1572-25-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>855.5599999999999</v>
+        <v>945.9400000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1572-26-CM26</t>
+          <t>5687-12-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.978.920-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>6652.5</v>
+        <v>8232.620000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5687-12-CM26</t>
+          <t>1572-26-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.978.920-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACIONES REGION ARICA-PARINACOTA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6368,13 +6368,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>8232.620000000001</v>
+        <v>6652.5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1572-25-CM26</t>
+          <t>1075963-3858-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>945.9400000000001</v>
+        <v>3788.59</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1075963-3858-CM26</t>
+          <t>3459-48-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3788.59</v>
+        <v>7067.42</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3459-48-CM26</t>
+          <t>1774-31-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>7067.42</v>
+        <v>7837.54</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1774-31-CM26</t>
+          <t>1110404-199-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>7837.54</v>
+        <v>1987.98</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1110404-197-CM26</t>
+          <t>1110404-202-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.473.108-5</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1374.31</v>
+        <v>2801.29</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1110404-199-CM26</t>
+          <t>1110404-201-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1987.98</v>
+        <v>843.13</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1110404-200-CM26</t>
+          <t>1110404-197-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2584.53</v>
+        <v>1374.31</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1110404-201-CM26</t>
+          <t>1110404-200-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>843.13</v>
+        <v>2584.53</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1110404-202-CM26</t>
+          <t>4232-34-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.473.108-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2801.29</v>
+        <v>2217.96</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4232-34-CM26</t>
+          <t>3185-41-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2217.96</v>
+        <v>1853.05</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3185-41-CM26</t>
+          <t>707409-37-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1853.05</v>
+        <v>1405.81</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>707409-37-CM26</t>
+          <t>707409-38-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1405.81</v>
+        <v>763.8200000000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>707409-38-CM26</t>
+          <t>1173457-12-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>763.8200000000001</v>
+        <v>1038.93</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1173457-12-CM26</t>
+          <t>1110404-295-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1038.93</v>
+        <v>2564.15</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1110404-295-CM26</t>
+          <t>5420-34-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2564.15</v>
+        <v>2365.74</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5420-34-CM26</t>
+          <t>5420-35-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2365.74</v>
+        <v>2080.6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5420-35-CM26</t>
+          <t>2021-66-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2080.6</v>
+        <v>7324.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2021-66-CM26</t>
+          <t>2366-199-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7324.5</v>
+        <v>1851.87</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1075963-5093-CM26</t>
+          <t>3390-128-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3870.52</v>
+        <v>875.48</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2366-199-CM26</t>
+          <t>1075963-5093-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1851.87</v>
+        <v>3870.52</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3390-128-CM26</t>
+          <t>2585-284-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>875.48</v>
+        <v>2323.03</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2585-284-CM26</t>
+          <t>2585-297-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2323.03</v>
+        <v>1786.77</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2585-297-CM26</t>
+          <t>1110404-330-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1786.77</v>
+        <v>1467.05</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1110404-330-CM26</t>
+          <t>548849-44-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7792,22 +7792,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1467.05</v>
+        <v>2184.29</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>548849-44-CM26</t>
+          <t>1110404-368-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7848,27 +7848,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2184.29</v>
+        <v>1299.37</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1110404-368-CM26</t>
+          <t>720-109-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1299.37</v>
+        <v>1603.01</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>720-109-CM26</t>
+          <t>1151549-97-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7975,22 +7975,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1603.01</v>
+        <v>1094.51</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1151549-97-CM26</t>
+          <t>1347870-40-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8036,22 +8036,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1094.51</v>
+        <v>1012.82</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5550-17-CM26</t>
+          <t>1075963-6998-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8097,22 +8097,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>921.08</v>
+        <v>3952.26</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1347870-40-CM26</t>
+          <t>5702-368-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1012.82</v>
+        <v>1386.83</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1075963-6998-CM26</t>
+          <t>2585-456-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3952.26</v>
+        <v>11918.93</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5702-368-CM26</t>
+          <t>635-725-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8320,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1386.83</v>
+        <v>1075.28</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2585-456-CM26</t>
+          <t>5611-49-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8341,22 +8341,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>11918.93</v>
+        <v>3529.25</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>635-725-CM26</t>
+          <t>5611-48-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1075.28</v>
+        <v>1434.91</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5611-48-CM26</t>
+          <t>1110404-515-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1434.91</v>
+        <v>3195.96</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5611-49-CM26</t>
+          <t>1696-172-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3529.25</v>
+        <v>6126.6</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1110404-515-CM26</t>
+          <t>1084148-59-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3195.96</v>
+        <v>1011.31</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1696-172-CM26</t>
+          <t>837-395-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>6126.6</v>
+        <v>5069.17</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1084148-59-CM26</t>
+          <t>1572-61-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1011.31</v>
+        <v>1217.91</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1093870-8-CM26</t>
+          <t>2585-595-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>9923.43</v>
+        <v>21366.84</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1572-61-CM26</t>
+          <t>707409-67-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1217.91</v>
+        <v>923.7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2585-595-CM26</t>
+          <t>707409-66-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8900,12 +8900,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>21366.84</v>
+        <v>1040.72</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>707409-66-CM26</t>
+          <t>5702-496-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1040.72</v>
+        <v>1110.62</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>707409-67-CM26</t>
+          <t>1075963-8316-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9012,22 +9012,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>923.7</v>
+        <v>3812.94</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1075963-8316-CM26</t>
+          <t>5951-78-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3812.94</v>
+        <v>795.1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5702-496-CM26</t>
+          <t>5611-65-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9134,22 +9134,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9174,13 +9174,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1110.62</v>
+        <v>2960.24</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5951-78-CM26</t>
+          <t>1110404-670-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9195,22 +9195,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>795.1</v>
+        <v>2061.11</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5611-65-CM26</t>
+          <t>1110404-658-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9256,22 +9256,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2960.24</v>
+        <v>2054.44</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1110404-670-CM26</t>
+          <t>1075963-10005-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2061.11</v>
+        <v>5234.8</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1110404-658-CM26</t>
+          <t>5593-126-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2054.44</v>
+        <v>2824.68</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1108734-36-CM26</t>
+          <t>5611-73-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1011.71</v>
+        <v>1582.48</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2021-147-CM26</t>
+          <t>635-1139-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1257.79</v>
+        <v>1007.13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1075963-10005-CM26</t>
+          <t>1110404-839-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9556,27 +9556,27 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>5234.8</v>
+        <v>3207.31</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5593-126-CM26</t>
+          <t>1173041-42-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9622,22 +9622,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2824.68</v>
+        <v>959.4299999999999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5611-73-CM26</t>
+          <t>1075963-11434-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9678,27 +9678,27 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1582.48</v>
+        <v>4876.74</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>635-1139-CM26</t>
+          <t>5358-233-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1007.13</v>
+        <v>2164.28</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1110404-839-CM26</t>
+          <t>1075963-11744-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9845,13 +9845,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3207.31</v>
+        <v>834.65</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1173041-42-CM26</t>
+          <t>1151549-203-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9906,7 +9906,312 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>959.4299999999999</v>
+        <v>4809.99</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>3348-99-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>61.101.082-6</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>10881.79</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>5649-38-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>61.979.030-8</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>1398.19</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1337362-45-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>976.17</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2585-1057-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>13014.74</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>5750-77-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>9371.620000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M214"/>
+  <dimension ref="A1:M223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1339,7 +1339,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3390-30-CM25</t>
+          <t>3390-31-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.993.355-7</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3231.62</v>
+        <v>866.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3390-31-CM25</t>
+          <t>3390-30-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.993.355-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>866.85</v>
+        <v>3231.62</v>
       </c>
     </row>
     <row r="17">
@@ -2644,7 +2644,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>959257-3-CM25</t>
+          <t>1151549-155-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.999.050-1</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2684,32 +2684,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.993.355-7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1857.83</v>
+        <v>2234.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1151549-155-CM25</t>
+          <t>959257-3-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2734,12 +2730,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>61.999.050-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2749,22 +2745,26 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.993.355-7</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2234.18</v>
+        <v>1857.83</v>
       </c>
     </row>
     <row r="38">
@@ -5066,7 +5066,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1151549-279-CM25</t>
+          <t>1151549-278-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5125,13 +5125,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>765.08</v>
+        <v>2383.53</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1151549-278-CM25</t>
+          <t>1151549-279-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2383.53</v>
+        <v>765.08</v>
       </c>
     </row>
     <row r="76">
@@ -7285,7 +7285,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1079596-370-CM25</t>
+          <t>1093870-20-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5980.23</v>
+        <v>23221.69</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1093870-20-CM25</t>
+          <t>1079596-370-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>23221.69</v>
+        <v>5980.23</v>
       </c>
     </row>
     <row r="111">
@@ -8610,7 +8610,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1075963-2359-CM26</t>
+          <t>1346279-20-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8630,17 +8630,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8665,13 +8665,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>4217.3</v>
+        <v>3839.75</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1346279-20-CM26</t>
+          <t>1075963-2359-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8691,17 +8691,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3839.75</v>
+        <v>4217.3</v>
       </c>
     </row>
     <row r="132">
@@ -8988,7 +8988,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1075963-2497-CM26</t>
+          <t>1572-11-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9043,13 +9043,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3599.09</v>
+        <v>2260.65</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1572-11-CM26</t>
+          <t>1572-12-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9089,28 +9089,32 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2260.65</v>
+        <v>807.15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1572-12-CM26</t>
+          <t>1075963-2497-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9135,12 +9139,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9150,26 +9154,22 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>807.15</v>
+        <v>3599.09</v>
       </c>
     </row>
     <row r="139">
@@ -9362,7 +9362,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5420-18-CM26</t>
+          <t>2366-100-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2979.26</v>
+        <v>7484.94</v>
       </c>
     </row>
     <row r="143">
@@ -9488,7 +9488,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2366-107-CM26</t>
+          <t>5420-18-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9513,12 +9513,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9528,17 +9528,17 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9547,13 +9547,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1447.7</v>
+        <v>2979.26</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2366-100-CM26</t>
+          <t>2366-107-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>7484.94</v>
+        <v>1447.7</v>
       </c>
     </row>
     <row r="146">
@@ -9801,7 +9801,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1572-25-CM26</t>
+          <t>1572-26-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9856,13 +9856,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>945.9400000000001</v>
+        <v>6652.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5687-12-CM26</t>
+          <t>1572-25-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.978.920-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9917,13 +9917,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>8232.620000000001</v>
+        <v>945.9400000000001</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1572-26-CM26</t>
+          <t>5687-12-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.978.920-2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>81.056.900-k</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>6652.5</v>
+        <v>8232.620000000001</v>
       </c>
     </row>
     <row r="152">
@@ -10045,7 +10045,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3459-48-CM26</t>
+          <t>1774-31-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10085,12 +10085,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -10104,13 +10104,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>7067.42</v>
+        <v>7837.54</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1774-31-CM26</t>
+          <t>3459-48-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10150,12 +10150,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>7837.54</v>
+        <v>7067.42</v>
       </c>
     </row>
     <row r="155">
@@ -10236,7 +10236,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1110404-199-CM26</t>
+          <t>1110404-200-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10276,17 +10276,17 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10295,13 +10295,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1987.98</v>
+        <v>2584.53</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1110404-200-CM26</t>
+          <t>1110404-201-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10341,17 +10341,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10360,13 +10360,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2584.53</v>
+        <v>843.13</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1110404-201-CM26</t>
+          <t>1110404-202-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10406,32 +10406,28 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.473.108-5</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>843.13</v>
+        <v>2801.29</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1110404-202-CM26</t>
+          <t>1110404-199-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10471,22 +10467,26 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Inversiones Corp Premier Ltda</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.473.108-5</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2801.29</v>
+        <v>1987.98</v>
       </c>
     </row>
     <row r="160">
@@ -10622,7 +10622,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>707409-37-CM26</t>
+          <t>707409-38-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10662,28 +10662,32 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>93.558.000-5</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1405.81</v>
+        <v>763.8200000000001</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>707409-38-CM26</t>
+          <t>707409-37-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10723,26 +10727,22 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>763.8200000000001</v>
+        <v>1405.81</v>
       </c>
     </row>
     <row r="164">
@@ -11073,7 +11073,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1075963-5093-CM26</t>
+          <t>2366-199-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11113,22 +11113,26 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+          <t>78.067.906-9</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3870.52</v>
+        <v>1851.87</v>
       </c>
     </row>
     <row r="170">
@@ -11199,7 +11203,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2366-199-CM26</t>
+          <t>1075963-5093-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11224,12 +11228,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11239,26 +11243,22 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1851.87</v>
+        <v>3870.52</v>
       </c>
     </row>
     <row r="172">
@@ -12032,7 +12032,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5611-48-CM26</t>
+          <t>5611-49-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12072,28 +12072,32 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1434.91</v>
+        <v>3529.25</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5611-49-CM26</t>
+          <t>5611-48-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12133,26 +12137,22 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3529.25</v>
+        <v>1434.91</v>
       </c>
     </row>
     <row r="186">
@@ -12674,7 +12674,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5702-496-CM26</t>
+          <t>1075963-8316-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12714,32 +12714,28 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1110.62</v>
+        <v>3812.94</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1075963-8316-CM26</t>
+          <t>5702-496-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12764,12 +12760,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12779,22 +12775,26 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3812.94</v>
+        <v>1110.62</v>
       </c>
     </row>
     <row r="196">
@@ -13560,7 +13560,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1075963-11744-CM26</t>
+          <t>1151549-203-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13580,17 +13580,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13600,28 +13600,32 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>834.65</v>
+        <v>4809.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1151549-203-CM26</t>
+          <t>1075963-11744-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13641,17 +13645,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13661,26 +13665,22 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>4809.99</v>
+        <v>834.65</v>
       </c>
     </row>
     <row r="210">
@@ -13812,7 +13812,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1337362-45-CM26</t>
+          <t>2585-1057-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13832,17 +13832,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13852,28 +13852,32 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>YANULAQUE Y CIA LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>81.056.900-k</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>976.17</v>
+        <v>13014.74</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2585-1057-CM26</t>
+          <t>1337362-45-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13893,17 +13897,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13913,26 +13917,22 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>YANULAQUE Y CIA LTDA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>13014.74</v>
+        <v>976.17</v>
       </c>
     </row>
     <row r="214">
@@ -13994,6 +13994,575 @@
       </c>
       <c r="M214" s="2" t="n">
         <v>9371.620000000001</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>5611-87-CM26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>61.813.000-2</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>2156.89</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>5965-310-CM26</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="n">
+        <v>2733.39</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>3390-382-CM26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>1032.54</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>707409-101-CM26</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>1520.25</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>707409-102-CM26</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>1252.8</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1075963-13165-CM26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>3615.44</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>3390-396-CM26</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="n">
+        <v>1009.82</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2366-604-CM26</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>YANULAQUE Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>81.056.900-k</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>8884.450000000001</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>5702-770-CM26</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>1010.93</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/arica-y-parinacota.xlsx
@@ -14653,7 +14653,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
